--- a/data/trans_dic/KIDM_A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_A_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,54</t>
+          <t>0,0; 12,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,51</t>
+          <t>0,0; 13,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,72</t>
+          <t>0,0; 11,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,4</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,26</t>
+          <t>0,0; 6,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,13</t>
+          <t>0,0; 7,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,82</t>
+          <t>0,0; 12,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,23</t>
+          <t>0,0; 10,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,9</t>
+          <t>0,0; 7,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,65</t>
+          <t>0,0; 15,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,67</t>
+          <t>0,0; 13,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,78</t>
+          <t>0,0; 9,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 4,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,43</t>
+          <t>0,0; 7,94</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,66</t>
+          <t>0,0; 16,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,02</t>
+          <t>0,0; 6,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,46</t>
+          <t>0,0; 10,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 10,97</t>
+          <t>1,32; 10,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,16</t>
+          <t>0,0; 11,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,83</t>
+          <t>0,0; 10,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,5</t>
+          <t>0,0; 16,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 10,03</t>
+          <t>1,7; 10,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,28</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 7,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,09</t>
+          <t>0,0; 10,74</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,68</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 10,82</t>
+          <t>1,71; 9,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,86</t>
+          <t>0,63; 6,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,45</t>
+          <t>0,0; 7,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 10,54</t>
+          <t>2,25; 10,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,08</t>
+          <t>1,17; 10,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,67</t>
+          <t>2,83; 8,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,77</t>
+          <t>1,42; 5,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,62</t>
+          <t>0,0; 9,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,23</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,1</t>
+          <t>0,0; 7,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,96</t>
+          <t>0,0; 7,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 10,31</t>
+          <t>1,01; 9,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,75</t>
+          <t>0,65; 5,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,19</t>
+          <t>1,41; 6,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,4</t>
+          <t>0,0; 9,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,12</t>
+          <t>0,0; 22,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 12,9</t>
+          <t>1,57; 13,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 19,52</t>
+          <t>2,28; 18,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 13,96</t>
+          <t>2,12; 12,99</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,83</t>
+          <t>1,13; 10,09</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,81</t>
+          <t>1,01; 3,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,11</t>
+          <t>1,93; 5,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,12</t>
+          <t>0,76; 3,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,26</t>
+          <t>0,33; 3,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,75</t>
+          <t>0,93; 3,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,86</t>
+          <t>2,22; 5,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,69</t>
+          <t>0,8; 3,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,3</t>
+          <t>0,37; 3,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,17</t>
+          <t>1,18; 3,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,11</t>
+          <t>2,44; 4,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,77</t>
+          <t>0,94; 2,74</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,52</t>
+          <t>0,64; 2,66</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4686</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4641</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4222</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5295</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4278</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4759</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1451</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1451</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3008</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3077</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3444</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4457</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4119</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5400</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2696</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2759</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4890</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3366</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4389</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2933</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2518</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>664; 5407</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3234</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3659</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4504</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1321; 7804</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4162</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4492</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4537</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3682</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2685</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5397</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3473</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>9079</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6158</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4726</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1366; 7908</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>655; 6596</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5036</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2143; 9918</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1041; 8926</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4143</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>4948; 14623</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2745; 11585</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4647</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2786</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2659</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>4153</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4587</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4687</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5221</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2207</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4462</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>667; 6586</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>698; 6034</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1887; 8406</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4463</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1966</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1586</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1884</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3471</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3605</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4749</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>556; 4916</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>823; 6750</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2704</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1196; 7333</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>747; 6685</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>5401</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>9344</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>5051</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2650</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>5634</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10715</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5546</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>11036</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>20059</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>10597</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2608; 10190</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5365; 15940</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2328; 10299</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>692; 6571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2653; 10353</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6459; 17138</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2459; 11739</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>985; 8152</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>6414; 17504</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>13857; 28310</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5796; 16853</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>3031; 12651</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/KIDM_A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_A_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,72</t>
+          <t>0,0; 13,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,74</t>
+          <t>0,0; 12,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,88</t>
+          <t>0,0; 11,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,59</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 7,4</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,28</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,11</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,26</t>
+          <t>0,0; 17,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,38</t>
+          <t>0,0; 10,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,37</t>
+          <t>0,0; 6,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,28</t>
+          <t>0,0; 16,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,91</t>
+          <t>0,0; 13,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,97</t>
+          <t>0,0; 9,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,2</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,94</t>
+          <t>0,0; 7,5</t>
         </is>
       </c>
     </row>
@@ -997,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,04</t>
+          <t>0,0; 16,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,93</t>
+          <t>0,0; 8,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,23</t>
+          <t>0,0; 11,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 10,75</t>
+          <t>1,32; 10,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,25</t>
+          <t>0,0; 14,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,06</t>
+          <t>0,0; 11,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,27</t>
+          <t>0,0; 13,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 10,05</t>
+          <t>1,59; 9,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,36</t>
+          <t>0,0; 7,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,74</t>
+          <t>0,0; 11,17</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,63</t>
+          <t>0,0; 5,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 9,92</t>
+          <t>1,7; 10,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,33</t>
+          <t>0,64; 6,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,41</t>
+          <t>0,0; 6,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 10,41</t>
+          <t>2,64; 10,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,0</t>
+          <t>1,23; 9,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 8,36</t>
+          <t>2,9; 8,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,99</t>
+          <t>1,39; 5,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,65</t>
+          <t>0,0; 9,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>0,0; 7,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,48</t>
+          <t>0,0; 6,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 5,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,38</t>
+          <t>0,0; 7,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,96</t>
+          <t>1,21; 10,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,59</t>
+          <t>0,59; 5,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,28</t>
+          <t>1,44; 6,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,54</t>
+          <t>0,0; 9,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,51</t>
+          <t>0,0; 22,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 13,91</t>
+          <t>1,6; 13,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 18,71</t>
+          <t>2,38; 18,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 4,63</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 12,99</t>
+          <t>2,31; 13,28</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,09</t>
+          <t>1,31; 10,36</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,94</t>
+          <t>1,01; 3,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,75</t>
+          <t>1,88; 5,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,35</t>
+          <t>0,63; 2,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,16</t>
+          <t>0,32; 3,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,63</t>
+          <t>0,9; 3,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,88</t>
+          <t>2,25; 5,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,81</t>
+          <t>0,88; 3,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,04</t>
+          <t>0,4; 3,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,22</t>
+          <t>1,17; 3,12</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,98</t>
+          <t>2,34; 4,94</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,74</t>
+          <t>1,0; 2,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,66</t>
+          <t>0,57; 2,61</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4686</t>
+          <t>0; 4947</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4641</t>
+          <t>0; 4380</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4222</t>
+          <t>0; 4115</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5295</t>
+          <t>0; 4722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4278</t>
+          <t>0; 5040</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4759</t>
+          <t>0; 4103</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2135,27 +2135,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3008</t>
+          <t>0; 4294</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3077</t>
+          <t>0; 3224</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3444</t>
+          <t>0; 3119</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4457</t>
+          <t>0; 4759</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4119</t>
+          <t>0; 4107</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2175,22 +2175,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5400</t>
+          <t>0; 5305</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2696</t>
+          <t>0; 3007</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2759</t>
+          <t>0; 2721</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4890</t>
+          <t>0; 4618</t>
         </is>
       </c>
     </row>
@@ -2343,17 +2343,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4389</t>
+          <t>0; 4534</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2933</t>
+          <t>0; 3602</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2518</t>
+          <t>0; 2831</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2363,42 +2363,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>664; 5407</t>
+          <t>665; 5415</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3234</t>
+          <t>0; 4266</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3659</t>
+          <t>0; 4129</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4504</t>
+          <t>0; 3855</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1321; 7804</t>
+          <t>1235; 7216</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4162</t>
+          <t>0; 4189</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4492</t>
+          <t>0; 4473</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4537</t>
+          <t>0; 4716</t>
         </is>
       </c>
     </row>
@@ -2551,22 +2551,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4726</t>
+          <t>0; 4569</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1366; 7908</t>
+          <t>1357; 8579</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>655; 6596</t>
+          <t>664; 6942</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5036</t>
+          <t>0; 4090</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2143; 9918</t>
+          <t>2518; 9916</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1041; 8926</t>
+          <t>1100; 8907</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4143</t>
+          <t>0; 4075</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4948; 14623</t>
+          <t>5072; 15422</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2745; 11585</t>
+          <t>2698; 11238</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 4647</t>
+          <t>0; 3925</t>
         </is>
       </c>
     </row>
@@ -2759,32 +2759,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4587</t>
+          <t>0; 4679</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4687</t>
+          <t>0; 4833</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5221</t>
+          <t>0; 4438</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2207</t>
+          <t>0; 2106</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4462</t>
+          <t>0; 4762</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>667; 6586</t>
+          <t>797; 7069</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2799,22 +2799,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>698; 6034</t>
+          <t>642; 6356</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1887; 8406</t>
+          <t>1926; 8547</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4463</t>
+          <t>0; 4295</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 1966</t>
+          <t>0; 2304</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3605</t>
+          <t>0; 3570</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4749</t>
+          <t>0; 4793</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>556; 4916</t>
+          <t>566; 4866</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3002,17 +3002,17 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>823; 6750</t>
+          <t>859; 6631</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 2704</t>
+          <t>0; 3198</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1196; 7333</t>
+          <t>1306; 7498</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>747; 6685</t>
+          <t>870; 6862</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2608; 10190</t>
+          <t>2603; 9856</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5365; 15940</t>
+          <t>5201; 15487</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2328; 10299</t>
+          <t>1944; 8936</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>692; 6571</t>
+          <t>675; 6567</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2653; 10353</t>
+          <t>2563; 10747</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6459; 17138</t>
+          <t>6543; 16747</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2459; 11739</t>
+          <t>2708; 11408</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>985; 8152</t>
+          <t>1075; 8618</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6414; 17504</t>
+          <t>6385; 16967</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13857; 28310</t>
+          <t>13280; 28088</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5796; 16853</t>
+          <t>6169; 17519</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3031; 12651</t>
+          <t>2699; 12428</t>
         </is>
       </c>
     </row>
